--- a/www/download/COUNTRY.MEX.EXI382.xlsx
+++ b/www/download/COUNTRY.MEX.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>México</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3285</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>70.817</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>31.719</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>33.804</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>35.787</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>36.712</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>37.125</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>37.891</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>38.798</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>39.085</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>40.401</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>40.54</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>41.885</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>42.602</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>44.555</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>45.579</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>46.604</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>48.647</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>50.842</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>57.78</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>55.003</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>48.969</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>56.061</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>57.318</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>62.721</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>64.147</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>50.717</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>18.311</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20.096</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>20.983</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>22.865</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24.157</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>24.022</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>24.389</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>24.662</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>25.517</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>26.009</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>27.307</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>27.833</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>28.612</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>36.355</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>30.839</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>32.174</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>33.853</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>39.18</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>37.425</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>32.214</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>37.858</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>39.253</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>43.017</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>44.294</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>166944.645</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>73030.156</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>78639.907</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>83734.201</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>84392.359</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>86949.92</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>86773.862</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>85949.043</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>89434.235</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>88114.403</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>91242.593</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>91776.679</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>94921.542</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>96536.335</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>101615.166</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>103685.902</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>106272.579</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>107328.261</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>111338.223</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>116332.785</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>132673.529</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>126267.684</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>111749.052</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>129687.637</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>132697.752</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>145760.456</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>149205.754</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>119859.165</t>
+          <t>128694081616.882</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10129.794</t>
+          <t>60994917953.879</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13725.005</t>
+          <t>66727107392.5173</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13760.457</t>
+          <t>73195520428.8033</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17575.637</t>
+          <t>71482028972.7102</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19230.906</t>
+          <t>77743985186.7404</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22880.51</t>
+          <t>77191497545.3424</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22018.721</t>
+          <t>74710370718.5699</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22171.321</t>
+          <t>74063604392.4256</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22438.295</t>
+          <t>74004709413.7128</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23771.831</t>
+          <t>75823262542.2051</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>25300.633</t>
+          <t>76735189644.5972</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>28123.928</t>
+          <t>75462980037.8306</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>28829.067</t>
+          <t>79199533410.6709</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>30593.764</t>
+          <t>79672064448.8337</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>47248.538</t>
+          <t>81265188061.621</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>63967.049</t>
+          <t>84527069824.0737</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>33603.937</t>
+          <t>88365737353.3777</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>34804.515</t>
+          <t>93428753538.7746</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>76941.775</t>
+          <t>93771775488.3795</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>89456.267</t>
+          <t>107008701119.281</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>85583.005</t>
+          <t>100659356818.268</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>73017.892</t>
+          <t>91355189991.6672</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>87639.856</t>
+          <t>106453877679.428</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>90996.664</t>
+          <t>107553162727.586</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>100173.787</t>
+          <t>116131647211.682</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>103350.219</t>
+          <t>128055284398.027</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30097432618.139</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>15452733975.1805</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>16251505783.1797</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>19576148988.6894</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>18248517136.7634</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>17309256800.3623</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16724768870.4168</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16995260217.2002</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>16148288134.8612</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>15611070721.7879</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>16231230802.0837</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15855159441.148</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>14964772634.387</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>15358329336.856</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>13766358570.3633</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>13466507413.941</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>14129544131.0916</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>12845430472.9965</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>12325394183.4743</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>12017667520.6273</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>14137322249.8402</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>11396310066.2123</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>10698309835.0953</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10897525413.3173</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>12251150665.3009</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12961580584.8441</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>11042110743.5489</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>53986456.1423477</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>43137671.0511464</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>21036989.2057965</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>23046642.439174</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>17535227.1304932</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>14563715.4229728</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12554392.3683547</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11950833.879124</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>16735150.9896689</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>13546125.7745661</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12806713.6065579</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>11084757.6737109</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>11469488.5031782</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>11408449.1208706</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>13843125.1148722</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>11549349.6938501</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>11690305.0335339</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>12069792.4311659</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>13386863.8482068</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>17799657.487153</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>3425642730943454</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>17036868.9701863</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>-1954138195096874</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>159652169390.215</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>152421926980.605</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>177347908459.034</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>185388791394.604</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>311177.577710037</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>308959.412693899</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>366561.313786031</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>410595.560273308</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>422613.050139538</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>532638.938489032</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>524934.730120079</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>493654.685427091</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>463283.626981525</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>437410.466545037</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>481073.840893657</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>514810.869030501</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>548368.36242551</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>551932.325449173</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>578048.272072113</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>675383.656115263</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>719062.942185948</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>803620.527829802</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>802473.994345973</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>863798.032920876</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>1227399.50234872</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>985447.604666279</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>869131.338422097</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1056232.00185016</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1165856.20821547</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>1192779.46180961</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1205804.97506051</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>479720.398585205</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>463504.79937071</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>552275.179753313</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>622816.366321369</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>641572.286255935</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>834100.715444276</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>831564.819582885</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>780173.259858267</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>710475.977835265</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>693751.360378365</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>762006.483905948</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>824927.069022059</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>840500.042186342</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>886362.332832219</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>893534.082069594</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1051031.91121256</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1138098.73652695</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1313234.07266964</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1356303.27636658</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1409037.09474814</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1816381.43794162</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1557344.9750256</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1494305.12394434</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1693516.69028747</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1823012.20551969</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1872559.75404425</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2027199.68914797</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2.98237173789849</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.344465903815501</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.155462565555947</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.29708049280087</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.0368731405276166</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.111018585129776</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.368061357214527</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.29558010401661</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.37298274683175</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.437332224029022</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.464573530491242</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.595735009413236</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.879342151536122</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.877096549219535</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.22235704842003</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.5085962935747</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.52718420400042</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.61602264483492</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.82380542820213</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>5.40238836684991</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>5.32766694094312</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>6.50971186747004</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>5.82518017301614</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7.04217952035378</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>6.42760139745292</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>6.72851629661521</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>8.35964336356013</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>593.43744313761</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>843.881384659192</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>808.69758424297</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>932.943926031142</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>815.029796193045</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>757.019759472958</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>692.336336068635</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>707.484367195589</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>662.116296137441</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>633.003569140221</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>636.092298971588</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>609.59343318756</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>548.023665694358</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>551.804854573195</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>481.142695334124</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>414.738185640957</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>388.656907233489</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>416.533354724079</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>383.087921957511</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>354.994000098892</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>360.831197684492</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>304.512020959544</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>332.102744859442</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>287.853977307371</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>312.105121778797</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>301.311894718615</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>249.288540650327</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>5377619345.45232</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>-307249534.993378</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>-1555972018.41579</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>-3901753881.12256</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>-3193595766.86271</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>-3051730745.86009</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>-1362914899.02339</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>11276064.8575</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1564554137.45991</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>483720499.937362</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>995724328.515101</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>2184086198.55173</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>-121777354.554182</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>1379744191.13899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>-2659203922.29336</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>-1413996004.77166</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>-1011430227.68653</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>-401178643.483351</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>-13023791.4652571</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>-2727605660.89462</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>-4675003996.73335</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>-6559736920.87506</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>-6302297713.05892</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>-9420881718.18273</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>-7079845331.40411</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>-8348839381.73325</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>-10567063328.1073</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8003627523.46974</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>21204398.7133492</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-1324263078.64408</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-3616626061.16721</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-2979264731.20272</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-3051684028.83094</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1144169390.68139</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>152395594.238292</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-1480433262.62887</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>623521551.013457</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1079201476.07918</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2561506959.59178</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>358293811.194442</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2151429516.39528</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-1788460244.80235</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-485403983.19326</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>115235718.652538</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>748651811.912517</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1191057530.00046</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-1691611386.07186</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-3648549552.49425</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-5557234465.71568</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-5010219142.09006</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-8167696015.47622</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-5989148357.97252</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-7165492745.68321</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-7970167677.73099</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-2626008178.01742</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-328453933.706727</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-231708939.771709</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-285127819.95535</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-214331035.659987</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-46717.0291558502</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-218745508.341994</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-141119529.380792</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-84120874.8310369</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-139801051.076095</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-83477147.564079</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-377420761.040047</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-480071165.748624</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-771685325.256288</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-870743677.491009</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-928592021.578396</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-1126665946.33907</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-1149830455.39587</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-1204081321.46572</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-1035994274.82276</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-1026454444.2391</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-1002502455.15938</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1292078570.96886</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-1253185702.70651</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1090696973.43158</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-1183346636.05004</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-2596895650.3763</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>2363.28850176196</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>553.193020779487</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>682.975383037662</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>655.784484730232</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>784.977087983824</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>841.063022084929</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>947.15858757099</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>916.602670041387</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>909.074250992848</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>909.836427850623</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.155</t>
+          <t>931.603944023109</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>972.749582845799</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1029.92397497875</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1035.79098836193</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1069.2708602716</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1455.14886094376</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1759.52141120311</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1089.66068828725</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1081.76575350229</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.681</t>
+          <t>2272.80945653467</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>1.759</t>
+          <t>2283.21964084907</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>2286.79753758718</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2266.6610696189</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.791</t>
+          <t>2314.97336115372</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>2318.19243867641</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>2328.69388869682</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>2333.25183510942</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>2357.40263793611</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>2302.38138174111</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>2326.34227800793</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>2339.76111770924</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>2298.78020146148</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>2342.08538720468</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>2290.06745593925</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>2265.97319293549</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2305.12487757102</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>2254.41286110094</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>2258.44089335158</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>2263.85493339959</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>2266.22025813217</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>2266.01008405675</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>2334.38700473396</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>2327.15969359019</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>2331.607666672</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>2302.99376874858</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>2288.70599916133</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>2288.10211267766</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>2296.20189802576</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>2295.63394577267</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>2282.02457370669</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>2313.34316566392</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>2315.11729262209</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>2323.95674448238</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>2326.00836407611</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>85489.0915645799</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>98273.395553469</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>126089.615022315</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>135508.981031438</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>162689.194385949</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>227337.195342496</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>227340.15653758</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>214969.353302351</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>178708.463230891</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>185523.113221414</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>212076.041610233</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>243663.814757405</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>242511.102516433</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>234182.002592221</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>197785.630595818</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>271876.293536631</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>300689.06298278</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>344592.374993757</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>337064.448256779</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>358926.664893208</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>420552.250752948</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>417474.57241584</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>454781.690697389</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>483497.161069698</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>522848.396507612</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>534721.984678041</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>555099.573018315</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12356808043.3919</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7523367465.50241</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8926023398.4032</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10040648051.6613</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10852940868.965</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>12139408716.0616</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11604297153.1497</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11425443561.2574</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>12047460287.4903</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>12522349237.164</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>12978254188.4791</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12891214378.8683</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>12897459487.0622</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>12971199759.0528</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>14255385162.7794</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>15460028346.8193</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>16447329166.4265</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>16206526135.3689</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>16489105495.5354</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>16668441268.9748</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>19751050624.225</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>23108164602.9647</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>23680787709.9412</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>26682469152.3005</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>26212369845.5842</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>28900456876.6582</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>31688319210.9218</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>78276.2297794427</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>91481.3916410679</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>126741.308204522</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>146777.209183061</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>172743.56074501</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>243534.323031181</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>247755.66912679</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>231881.594409487</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>191121.98947569</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>200506.225396739</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>225758.382657695</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>258469.660594191</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>260186.608307179</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>257759.391303135</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>211922.484898541</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>286332.152429924</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>316417.9833421</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>359810.531187851</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>351543.559984335</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>374365.895180292</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>448946.081963002</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>442782.45660902</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>479586.696928473</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>509473.005270752</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>523212.02986823</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>536533.476003124</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>556668.56509584</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>166944.645</t>
+          <t>13648151924.2462</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>73030.156</t>
+          <t>5836403508.18705</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78639.907</t>
+          <t>7492040339.0708</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>83734.201</t>
+          <t>8261809429.61403</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>84392.359</t>
+          <t>9503757207.21153</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>86949.92</t>
+          <t>11600509727.9347</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>86773.862</t>
+          <t>13533975475.4101</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>85949.043</t>
+          <t>14266704981.6792</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>89434.235</t>
+          <t>12591686904.7656</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>88114.403</t>
+          <t>15753820306.3537</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>91242.593</t>
+          <t>16262358052.0028</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>91776.679</t>
+          <t>17278287543.4037</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>94921.542</t>
+          <t>14970668933.8378</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>96536.335</t>
+          <t>17581973960.7982</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>101615.166</t>
+          <t>13677004758.0472</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>103685.902</t>
+          <t>15828468892.164</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>106272.579</t>
+          <t>17249691270.1384</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>107328.261</t>
+          <t>17464601803.571</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>111338.223</t>
+          <t>18134715451.8831</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>116332.785</t>
+          <t>15582119851.7493</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>132673.529</t>
+          <t>17820733010.7537</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>126267.684</t>
+          <t>19232494105.3215</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>111749.052</t>
+          <t>19767776585.0345</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>129687.637</t>
+          <t>19843318956.386</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>132697.752</t>
+          <t>19165712387.7743</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>145760.456</t>
+          <t>20727407015.9222</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>149205.754</t>
+          <t>21274130741.9715</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>119859.165</t>
+          <t>7212.86178513719</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10129.794</t>
+          <t>6792.0039124012</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13725.005</t>
+          <t>-651.69318220683</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13760.457</t>
+          <t>-11268.2281516232</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17575.637</t>
+          <t>-10054.3663590604</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19230.906</t>
+          <t>-16197.1276886853</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>22880.51</t>
+          <t>-20415.5125892101</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22018.721</t>
+          <t>-16912.2411071358</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22171.321</t>
+          <t>-12413.5262447996</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22438.295</t>
+          <t>-14983.1121753253</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23771.831</t>
+          <t>-13682.3410474618</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>25300.633</t>
+          <t>-14805.8458367863</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>28123.928</t>
+          <t>-17675.5057907455</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>28829.067</t>
+          <t>-23577.3887109141</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>30593.764</t>
+          <t>-14136.8543027225</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>47248.538</t>
+          <t>-14455.8588932928</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>63967.049</t>
+          <t>-15728.9203593205</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>33603.937</t>
+          <t>-15218.1561940931</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>34804.515</t>
+          <t>-14479.1117275555</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>76941.775</t>
+          <t>-15439.2302870838</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>89456.267</t>
+          <t>-28393.8312100537</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>85583.005</t>
+          <t>-25307.8841931794</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>73017.892</t>
+          <t>-24805.006231084</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>87639.856</t>
+          <t>-25975.8442010537</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>90996.664</t>
+          <t>-363.633360618347</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>100173.787</t>
+          <t>-1811.49132508246</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>103350.219</t>
+          <t>-1568.99207752518</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>129934.245</t>
+          <t>-1291343880.85432</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>61609.286</t>
+          <t>1686963957.31536</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>67328.523</t>
+          <t>1433983059.3324</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>73859.581</t>
+          <t>1778838622.04727</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>71893.988</t>
+          <t>1349183661.75352</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>78014.608</t>
+          <t>538898988.126943</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>77101.341</t>
+          <t>-1929678322.2604</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>74588.337</t>
+          <t>-2841261420.42181</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>74305.814</t>
+          <t>-544226617.275309</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>73875.373</t>
+          <t>-3231471069.18968</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>75732.143</t>
+          <t>-3284103863.5237</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>76536.54</t>
+          <t>-4387073164.53537</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>75754.032</t>
+          <t>-2073209446.77558</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>79013.697</t>
+          <t>-4610774201.74538</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>79716.012</t>
+          <t>578380404.73221</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>81182.072</t>
+          <t>-368440545.344775</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>84300.952</t>
+          <t>-802362103.711846</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>88131.027</t>
+          <t>-1258075668.20207</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>93394.714</t>
+          <t>-1645609956.34766</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>94132.593</t>
+          <t>1086321417.22551</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>107276.952</t>
+          <t>1930317613.47126</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>100830.707</t>
+          <t>3875670497.64317</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>91372.506</t>
+          <t>3913011124.90665</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>106772.656</t>
+          <t>6839150195.91454</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>108213.938</t>
+          <t>7046657457.80993</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>116671.706</t>
+          <t>8173049860.73595</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>128768.765</t>
+          <t>10414188468.9503</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>105982.686189061</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>125217.631915292</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>175418.602361093</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>187233.344600713</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>216539.365772194</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>278369.640293265</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>298422.428514062</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>281611.359275658</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>204922.838961746</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>191481.242208396</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>206859.044775771</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>217497.776282891</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>197677.839365579</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>189615.42288936</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>153332.748106968</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>180639.079910429</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>191424.379005668</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>196237.386334491</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>200938.418596757</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>200942.0499365</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>212037.819042574</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>194531.316522157</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>212567.093797724</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>205600.058322322</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>225940.75735832</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>1.573</t>
+          <t>227876.383287074</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1.703</t>
+          <t>220143.145954644</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>83479.278</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>40657.517</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>44288.748</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>48254.602</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>47086.258</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>49645.652</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>48728.009</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>47272.992</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>48295.025</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>46659.994</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>47869.131</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>47888.003</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>49234.395</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>49317.058</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>51541.738</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>52220.279</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>53405.106</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>54074.534</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>55278.304</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>57485.978</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>72309.937</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>63694.636</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>53134.837</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>66394.381</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>68782.602</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>73973.31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>76168.963</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>136674.879606049</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>162749.130710149</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>216716.55703049</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>244565.027743973</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>285317.483013017</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>355950.371655416</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>390274.806085421</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>381639.779334817</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>292795.66438923</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>278922.083194833</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>314956.675755881</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>340322.911289634</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>330244.222174807</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>323854.134752294</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>264927.958973443</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>313541.543055</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>338204.912887517</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>336222.341864539</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>340625.758600425</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>341690.447786755</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>419753.302984938</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>319776.467172331</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>335822.196954274</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>326463.593522806</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>363323.446242933</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>366572.744464772</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>367580.02423635</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>29520.744</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>15304.991</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>16085.851</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>19393.05</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>17994.155</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>16989.706</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>16319.494</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>16540.653</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>15826.162</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>15202.963</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>15789.959</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>15431.104</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>14636.511</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>14912.639</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>13436.906</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>13109.646</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>13754.038</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>12501.721</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>12058.044</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>11824.751</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>13811.36</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>11096.254</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>10518.313</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10742.542</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>12019.076</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12709.555</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>10774.418</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>306.02</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-33.81</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-14.68</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-29.04</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-2.33</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>13.19</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>40.09</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>47.59</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>50.55</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>63.96</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>92.15</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>93.32</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>127.68</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>260.41</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>365.08</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>168.79</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>188.64</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>550.68</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>547.7</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>671.28</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>594.2</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>715.82</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>657.1</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>688.18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>859.22</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>71.13</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>57.039</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>27.741</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>30.402</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>23.081</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>19.132</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>16.415</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>15.611</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>21.993</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>17.632</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>16.687</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>14.851</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>18.075</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>15.052</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>15.215</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>15.793</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>17.564</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>23.51</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>4550966367.835</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>22.464</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>-2596072592.284</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>212097.818</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>202492.464</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>235606.621</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>246288.886</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>195858.010705248</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>231939.391945543</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>321191.705674939</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>331673.056241552</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>405365.414006437</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>578103.207832282</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>649565.734294941</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>632583.238194723</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>519909.918390386</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>519818.072281409</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>586015.719804067</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>660974.362267681</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>672416.06144272</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>666524.995211468</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>581668.83515096</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>732664.22075978</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>775514.372159762</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>888070.867535464</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>914647.996563207</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>953707.707778704</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>951454.180730083</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>947334.994716008</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>991403.631098571</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>1016880.49976022</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1095652.16172218</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1111090.36583869</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1141445.79841133</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>119859165041.781</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>10129793999.9994</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13725004999.9792</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>13760456999.9863</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>17575636999.9589</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>19230905999.9865</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>22880509999.9617</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>22018720999.9896</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>22171321000.0323</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>22438295000.0217</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>23771831000.0259</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>25300633000.0687</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>28123927999.9577</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>28829066999.9896</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>30593763999.9243</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>47248537999.9497</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>63967049000.0046</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>33603937000.0113</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>34804515000.0256</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>76941774730.7342</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>89456266633.7735</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>85583004949.6026</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>73017892171.2759</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>87639855701.5156</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>90996663801.995</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>100173786779.859</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>103350218540.553</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>166944645218.944</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>73030155999.9829</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>78639907000.0012</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>83734200999.999</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>84392359000.003</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>86949920000.0032</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>86773861999.9959</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>85949042999.9945</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>89434234999.9895</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>88114403000.0022</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>91242593000.0253</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>91776679000.02</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>94921541999.9694</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>96536334999.9932</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>101615165999.976</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>103685901999.992</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>106272579000.015</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>107328260999.988</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>111338222999.983</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>116332785379.224</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>132673528934.628</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>126267684168.211</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>111749052297.274</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>129687636926.603</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>132697752132.336</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>145760456153.465</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>149205753836.131</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>83479278140.4863</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>40657516500.214</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>44288747797.553</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>48254601749.5842</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>47086258152.7858</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>49645651870.3693</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>48728008902.3658</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>47272992363.1543</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>48295025223.5038</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>46659994228.3753</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>47869130920.3728</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>47888002648.5093</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>49234394658.0311</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>49317058081.8392</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>51541737591.4704</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>52220279177.4722</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>53405105876.4323</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>54074533985.8808</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>55278304156.188</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>57485977844.2091</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>72309936534.9331</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>63694636483.596</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>53134836571.8513</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>66394380977.118</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>68782601728.8887</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>73973310256.7471</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>76168963440.8086</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>70817196.2364064</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>31719399.999993</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>33804099.9999971</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>35787499.9999912</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>36711799.9999954</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>37125000.0000127</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>37891400.0000086</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>37930299.9999972</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>38797999.9999952</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>39085300.0000061</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>40400699.9999983</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>40540000.0000002</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>41885400.0000001</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>42601900.0000071</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>43529700.0000035</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>44554699.9999954</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>45579100.0000023</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>46603799.9999924</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>48646799.9999921</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>50842479.7716238</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>57779557.2108438</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>55003405.2252661</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>48969258.9575233</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>56060699.8786464</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>57317939.162401</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>62720812.8978882</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>64146697.0370913</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>50717110.9039033</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>18311499.9999925</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20095899.9999893</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>20983199.9999923</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>22390000.0000014</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>22865000.0000174</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>24157000.0000099</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>24022099.9999873</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>24388899.9999921</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>24661900.0000136</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>25517099.9999933</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>26009399.9999992</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>27306800.0000078</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>27832900.0000104</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>28611800.000005</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>32469899.9999945</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>36354799.9999988</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>30838899.9999905</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>32173799.999994</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>33853156.7217459</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>39179877.8502566</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>37424828.1900382</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>32213855.5031311</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>37857824.7042282</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>39253282.9819557</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>43017155.3530884</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>44294497.9129124</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>166944645218.944</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>73030155999.9829</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>78639907000.0012</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>83734200999.999</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>84392359000.003</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>86949920000.0032</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>86773861999.9959</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>85949042999.9945</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>89434234999.9895</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>88114403000.0022</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>91242593000.0253</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>91776679000.02</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>94921541999.9694</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>96536334999.9932</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>101615165999.976</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>103685901999.992</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>106272579000.015</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>107328260999.988</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>111338222999.983</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>116332785379.224</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>132673528934.628</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>126267684168.211</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>111749052297.274</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>129687636926.603</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>132697752132.336</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>145760456153.465</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>149205753836.131</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>119859165041.781</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>10129793999.9994</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13725004999.9792</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13760456999.9863</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>17575636999.9589</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>19230905999.9865</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>22880509999.9617</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22018720999.9896</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>22171321000.0323</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>22438295000.0217</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>23771831000.0259</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>25300633000.0687</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>28123927999.9577</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>28829066999.9896</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>30593763999.9243</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>47248537999.9497</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>63967049000.0046</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>33603937000.0113</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>34804515000.0256</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>76941774730.7342</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>89456266633.7735</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>85583004949.6026</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>73017892171.2759</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>87639855701.5156</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>90996663801.995</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>100173786779.859</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>103350218540.553</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>631556.251565466</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>748400.396024058</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1022530.06486028</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1104867.60998382</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1307039.18265217</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1772074.64830654</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1909111.93654025</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1816071.06887321</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1403509.60312537</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1369580.80420273</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1534965.2165058</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1711376.64621006</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1682909.65764369</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1682421.84481655</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1409337.77529932</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1751039.88102694</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1878499.69185969</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2121474.1962553</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2140437.74611104</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2232986.74090023</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2336719.50948354</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2163846.77412707</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2337500.7478722</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2379799.41336283</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2568642.36090278</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>2627896.38704321</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2685606.21173541</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>169857.834476717</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>198065.806040171</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>265054.035538176</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>292227.472245097</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>342813.964568061</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>440149.557816257</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>472899.469796524</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>452175.381333986</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>336633.203428732</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>315626.665281696</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>350989.38549884</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>371039.695369626</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>348020.332168772</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>336071.049622191</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>275595.618826377</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>327370.54910382</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>351121.605053912</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>353875.813814656</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>360179.759434234</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>360861.204423394</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>450166.701084637</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>346366.472092868</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>370065.041784847</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>356274.241090623</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>395354.313725073</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>399403.56424292</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>397732.411402542</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
